--- a/Bosch.xlsx
+++ b/Bosch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\pycharm\bosch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\Bosch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874B729-D748-48B0-A6B9-A074F78F070C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAEE0BF-87B3-4C32-8E5C-06F8351A372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>配方名</t>
   </si>
@@ -190,6 +187,57 @@
   </si>
   <si>
     <t>etch time</t>
+  </si>
+  <si>
+    <t>B39</t>
+  </si>
+  <si>
+    <t>B40</t>
+  </si>
+  <si>
+    <t>瓶型</t>
+  </si>
+  <si>
+    <t>B42</t>
+  </si>
+  <si>
+    <t>B44</t>
+  </si>
+  <si>
+    <t>B45</t>
+  </si>
+  <si>
+    <t>B46</t>
+  </si>
+  <si>
+    <t>B47</t>
+  </si>
+  <si>
+    <t>B49</t>
+  </si>
+  <si>
+    <t>B50</t>
+  </si>
+  <si>
+    <t>B52</t>
+  </si>
+  <si>
+    <t>B53</t>
+  </si>
+  <si>
+    <t>B54</t>
+  </si>
+  <si>
+    <t>B56</t>
+  </si>
+  <si>
+    <t>B58</t>
+  </si>
+  <si>
+    <t>B60</t>
+  </si>
+  <si>
+    <t>B61</t>
   </si>
 </sst>
 </file>
@@ -231,12 +279,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -251,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +319,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -545,14 +606,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U47"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="16" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="20.08203125" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,7 +673,7 @@
       </c>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -672,7 +733,7 @@
       </c>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -732,7 +793,7 @@
       </c>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -792,7 +853,7 @@
       </c>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -852,7 +913,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -912,7 +973,7 @@
       </c>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -972,7 +1033,7 @@
       </c>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1018,7 +1079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1078,7 +1139,7 @@
       </c>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1134,7 +1195,7 @@
       </c>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -1194,7 +1255,7 @@
       </c>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1254,7 +1315,7 @@
       </c>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,7 +1375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1374,7 +1435,7 @@
       </c>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -1434,7 +1495,7 @@
       </c>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -1494,7 +1555,7 @@
       </c>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -1546,7 +1607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -1606,7 +1667,7 @@
       </c>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
@@ -1666,7 +1727,7 @@
       </c>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
@@ -1726,7 +1787,7 @@
       </c>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1786,7 +1847,7 @@
       </c>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
@@ -1846,7 +1907,7 @@
       </c>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -1906,7 +1967,7 @@
       </c>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -1966,7 +2027,7 @@
       </c>
       <c r="T24" s="1"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,7 +2087,7 @@
       </c>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
@@ -2086,7 +2147,7 @@
       </c>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
@@ -2146,7 +2207,7 @@
       </c>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
@@ -2206,7 +2267,7 @@
       </c>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>40</v>
       </c>
@@ -2266,7 +2327,7 @@
       </c>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
@@ -2326,7 +2387,7 @@
       </c>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
@@ -2385,6 +2446,988 @@
         <v>31.24</v>
       </c>
       <c r="T31" s="1"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="1">
+        <v>50</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>90</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="I32" s="1">
+        <v>308.2</v>
+      </c>
+      <c r="J32" s="1">
+        <v>3123</v>
+      </c>
+      <c r="K32" s="1">
+        <v>462.3</v>
+      </c>
+      <c r="L32" s="1">
+        <v>364.7</v>
+      </c>
+      <c r="M32" s="1">
+        <v>77.05</v>
+      </c>
+      <c r="N32" s="1">
+        <v>431.5</v>
+      </c>
+      <c r="O32" s="1">
+        <v>313.39999999999998</v>
+      </c>
+      <c r="P32" s="1">
+        <v>61.64</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>421.2</v>
+      </c>
+      <c r="R32" s="1">
+        <v>303.10000000000002</v>
+      </c>
+      <c r="S32" s="1">
+        <v>10</v>
+      </c>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="1">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D33" s="3">
+        <v>95</v>
+      </c>
+      <c r="E33" s="1">
+        <v>150</v>
+      </c>
+      <c r="F33" s="1">
+        <v>100</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>351.2</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1492</v>
+      </c>
+      <c r="K33" s="1">
+        <v>430.5</v>
+      </c>
+      <c r="L33" s="1">
+        <v>165</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>480.6</v>
+      </c>
+      <c r="O33" s="1">
+        <v>165</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>475.4</v>
+      </c>
+      <c r="R33" s="1">
+        <v>165</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="1"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100</v>
+      </c>
+      <c r="E34" s="3">
+        <v>500</v>
+      </c>
+      <c r="F34" s="3">
+        <v>450</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I34" s="1">
+        <v>485.4</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2494</v>
+      </c>
+      <c r="K34" s="1">
+        <v>434.1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>284.10000000000002</v>
+      </c>
+      <c r="M34" s="1">
+        <v>71.03</v>
+      </c>
+      <c r="N34" s="1">
+        <v>410.4</v>
+      </c>
+      <c r="O34" s="1">
+        <v>256.5</v>
+      </c>
+      <c r="P34" s="1">
+        <v>47.36</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>418.3</v>
+      </c>
+      <c r="R34" s="1">
+        <v>276.2</v>
+      </c>
+      <c r="S34" s="1">
+        <v>39.46</v>
+      </c>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="1">
+        <v>40</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D35" s="1">
+        <v>65</v>
+      </c>
+      <c r="E35" s="1">
+        <v>250</v>
+      </c>
+      <c r="F35" s="3">
+        <v>100</v>
+      </c>
+      <c r="G35" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I35" s="1">
+        <v>298.3</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2217</v>
+      </c>
+      <c r="K35" s="1">
+        <v>449.3</v>
+      </c>
+      <c r="L35" s="1">
+        <v>235.7</v>
+      </c>
+      <c r="M35" s="1">
+        <v>47.88</v>
+      </c>
+      <c r="N35" s="1">
+        <v>445.7</v>
+      </c>
+      <c r="O35" s="1">
+        <v>202.6</v>
+      </c>
+      <c r="P35" s="1">
+        <v>29.46</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>427.2</v>
+      </c>
+      <c r="R35" s="1">
+        <v>265.2</v>
+      </c>
+      <c r="S35" s="1">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D36" s="1">
+        <v>25</v>
+      </c>
+      <c r="E36" s="1">
+        <v>500</v>
+      </c>
+      <c r="F36" s="1">
+        <v>200</v>
+      </c>
+      <c r="G36" s="3">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>526.5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2211</v>
+      </c>
+      <c r="K36" s="1">
+        <v>503.9</v>
+      </c>
+      <c r="L36" s="1">
+        <v>270.8</v>
+      </c>
+      <c r="M36" s="1">
+        <v>67.69</v>
+      </c>
+      <c r="N36" s="1">
+        <v>488.9</v>
+      </c>
+      <c r="O36" s="1">
+        <v>229.4</v>
+      </c>
+      <c r="P36" s="1">
+        <v>48.89</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>473.8</v>
+      </c>
+      <c r="R36" s="1">
+        <v>282</v>
+      </c>
+      <c r="S36" s="1">
+        <v>30.08</v>
+      </c>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="1">
+        <v>15</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2400</v>
+      </c>
+      <c r="D37" s="1">
+        <v>35</v>
+      </c>
+      <c r="E37" s="1">
+        <v>350</v>
+      </c>
+      <c r="F37" s="1">
+        <v>400</v>
+      </c>
+      <c r="G37" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="I37" s="1">
+        <v>393.7</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2278</v>
+      </c>
+      <c r="K37" s="1">
+        <v>368.1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>262.39999999999998</v>
+      </c>
+      <c r="M37" s="1">
+        <v>61.96</v>
+      </c>
+      <c r="N37" s="1">
+        <v>346.3</v>
+      </c>
+      <c r="O37" s="1">
+        <v>240.6</v>
+      </c>
+      <c r="P37" s="1">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>320.8</v>
+      </c>
+      <c r="R37" s="1">
+        <v>251.5</v>
+      </c>
+      <c r="S37" s="1">
+        <v>25.51</v>
+      </c>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="5">
+        <v>30</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2700</v>
+      </c>
+      <c r="D38" s="5">
+        <v>25</v>
+      </c>
+      <c r="E38" s="5">
+        <v>50</v>
+      </c>
+      <c r="F38" s="5">
+        <v>200</v>
+      </c>
+      <c r="G38" s="6">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="I38" s="5">
+        <v>334</v>
+      </c>
+      <c r="J38" s="5">
+        <v>1587</v>
+      </c>
+      <c r="K38" s="5">
+        <v>354.1</v>
+      </c>
+      <c r="L38" s="5">
+        <v>168.3</v>
+      </c>
+      <c r="M38" s="5">
+        <v>20.09</v>
+      </c>
+      <c r="N38" s="5">
+        <v>349.1</v>
+      </c>
+      <c r="O38" s="5">
+        <v>168.3</v>
+      </c>
+      <c r="P38" s="5">
+        <v>12.56</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>354.1</v>
+      </c>
+      <c r="R38" s="5">
+        <v>168.3</v>
+      </c>
+      <c r="S38" s="5">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="1">
+        <v>50</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2400</v>
+      </c>
+      <c r="D39" s="1">
+        <v>25</v>
+      </c>
+      <c r="E39" s="1">
+        <v>200</v>
+      </c>
+      <c r="F39" s="1">
+        <v>450</v>
+      </c>
+      <c r="G39" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1">
+        <v>338.9</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2057</v>
+      </c>
+      <c r="K39" s="1">
+        <v>328.7</v>
+      </c>
+      <c r="L39" s="1">
+        <v>267.7</v>
+      </c>
+      <c r="M39" s="1">
+        <v>61</v>
+      </c>
+      <c r="N39" s="1">
+        <v>349.1</v>
+      </c>
+      <c r="O39" s="1">
+        <v>233.8</v>
+      </c>
+      <c r="P39" s="1">
+        <v>64.39</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>284.7</v>
+      </c>
+      <c r="R39" s="1">
+        <v>233.8</v>
+      </c>
+      <c r="S39" s="1">
+        <v>40.67</v>
+      </c>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="1">
+        <v>50</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D40" s="1">
+        <v>25</v>
+      </c>
+      <c r="E40" s="1">
+        <v>200</v>
+      </c>
+      <c r="F40" s="3">
+        <v>500</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I40" s="1">
+        <v>221</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1402</v>
+      </c>
+      <c r="K40" s="1">
+        <v>292.3</v>
+      </c>
+      <c r="L40" s="1">
+        <v>178.3</v>
+      </c>
+      <c r="M40" s="1">
+        <v>42.78</v>
+      </c>
+      <c r="N40" s="1">
+        <v>266.2</v>
+      </c>
+      <c r="O40" s="1">
+        <v>171.1</v>
+      </c>
+      <c r="P40" s="1">
+        <v>38.03</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>244.8</v>
+      </c>
+      <c r="R40" s="1">
+        <v>185.4</v>
+      </c>
+      <c r="S40" s="1">
+        <v>23.77</v>
+      </c>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+    </row>
+    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="5">
+        <v>20</v>
+      </c>
+      <c r="C41" s="5">
+        <v>3000</v>
+      </c>
+      <c r="D41" s="5">
+        <v>95</v>
+      </c>
+      <c r="E41" s="5">
+        <v>400</v>
+      </c>
+      <c r="F41" s="5">
+        <v>100</v>
+      </c>
+      <c r="G41" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="I41" s="5">
+        <v>375.5</v>
+      </c>
+      <c r="J41" s="5">
+        <v>2030</v>
+      </c>
+      <c r="K41" s="5">
+        <v>400</v>
+      </c>
+      <c r="L41" s="5">
+        <v>225</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5">
+        <v>534.6</v>
+      </c>
+      <c r="O41" s="5">
+        <v>225</v>
+      </c>
+      <c r="P41" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>578.5</v>
+      </c>
+      <c r="R41" s="5">
+        <v>225</v>
+      </c>
+      <c r="S41" s="5">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="1">
+        <v>30</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2800</v>
+      </c>
+      <c r="D42" s="1">
+        <v>75</v>
+      </c>
+      <c r="E42" s="3">
+        <v>500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>300</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="I42" s="1">
+        <v>361.9</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2659</v>
+      </c>
+      <c r="K42" s="1">
+        <v>440.6</v>
+      </c>
+      <c r="L42" s="1">
+        <v>304.2</v>
+      </c>
+      <c r="M42" s="1">
+        <v>78.67</v>
+      </c>
+      <c r="N42" s="1">
+        <v>430.1</v>
+      </c>
+      <c r="O42" s="1">
+        <v>272.7</v>
+      </c>
+      <c r="P42" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>430.1</v>
+      </c>
+      <c r="R42" s="1">
+        <v>262.2</v>
+      </c>
+      <c r="S42" s="1">
+        <v>20.98</v>
+      </c>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+    </row>
+    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="5">
+        <v>15</v>
+      </c>
+      <c r="C43" s="5">
+        <v>2900</v>
+      </c>
+      <c r="D43" s="5">
+        <v>25</v>
+      </c>
+      <c r="E43" s="5">
+        <v>50</v>
+      </c>
+      <c r="F43" s="5">
+        <v>150</v>
+      </c>
+      <c r="G43" s="6">
+        <v>2</v>
+      </c>
+      <c r="H43" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="I43" s="5">
+        <v>321.89999999999998</v>
+      </c>
+      <c r="J43" s="5">
+        <v>1000.9</v>
+      </c>
+      <c r="K43" s="5">
+        <v>314.5</v>
+      </c>
+      <c r="L43" s="5">
+        <v>107.9</v>
+      </c>
+      <c r="M43" s="5">
+        <v>14.89</v>
+      </c>
+      <c r="N43" s="5">
+        <v>316.3</v>
+      </c>
+      <c r="O43" s="5">
+        <v>104.2</v>
+      </c>
+      <c r="P43" s="5">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>323.8</v>
+      </c>
+      <c r="R43" s="5">
+        <v>189.8</v>
+      </c>
+      <c r="S43" s="5">
+        <v>7.44</v>
+      </c>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="1">
+        <v>30</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2200</v>
+      </c>
+      <c r="D44" s="1">
+        <v>90</v>
+      </c>
+      <c r="E44" s="1">
+        <v>500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I44" s="1">
+        <v>424</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1502</v>
+      </c>
+      <c r="K44" s="1">
+        <v>515.79999999999995</v>
+      </c>
+      <c r="L44" s="1">
+        <v>150</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>568.79999999999995</v>
+      </c>
+      <c r="O44" s="1">
+        <v>150</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>568.79999999999995</v>
+      </c>
+      <c r="R44" s="1">
+        <v>150</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="1">
+        <v>50</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2300</v>
+      </c>
+      <c r="D45" s="1">
+        <v>25</v>
+      </c>
+      <c r="E45" s="1">
+        <v>350</v>
+      </c>
+      <c r="F45" s="1">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I45" s="1">
+        <v>348.9</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1630</v>
+      </c>
+      <c r="K45" s="1">
+        <v>332.2</v>
+      </c>
+      <c r="L45" s="1">
+        <v>198.2</v>
+      </c>
+      <c r="M45" s="1">
+        <v>72.569999999999993</v>
+      </c>
+      <c r="N45" s="1">
+        <v>295.89999999999998</v>
+      </c>
+      <c r="O45" s="1">
+        <v>173.1</v>
+      </c>
+      <c r="P45" s="1">
+        <v>44.66</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>256.8</v>
+      </c>
+      <c r="R45" s="1">
+        <v>187</v>
+      </c>
+      <c r="S45" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="1">
+        <v>35</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2700</v>
+      </c>
+      <c r="D46" s="1">
+        <v>25</v>
+      </c>
+      <c r="E46" s="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="1">
+        <v>500</v>
+      </c>
+      <c r="G46" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="I46" s="1">
+        <v>233.4</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1962</v>
+      </c>
+      <c r="K46" s="1">
+        <v>301.10000000000002</v>
+      </c>
+      <c r="L46" s="1">
+        <v>270.7</v>
+      </c>
+      <c r="M46" s="1">
+        <v>67.67</v>
+      </c>
+      <c r="N46" s="1">
+        <v>294.3</v>
+      </c>
+      <c r="O46" s="1">
+        <v>236.8</v>
+      </c>
+      <c r="P46" s="1">
+        <v>57.52</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>216.5</v>
+      </c>
+      <c r="R46" s="1">
+        <v>196.2</v>
+      </c>
+      <c r="S46" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="1">
+        <v>25</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D47" s="1">
+        <v>25</v>
+      </c>
+      <c r="E47" s="1">
+        <v>250</v>
+      </c>
+      <c r="F47" s="1">
+        <v>100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I47" s="1">
+        <v>435.4</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1368</v>
+      </c>
+      <c r="K47" s="1">
+        <v>450</v>
+      </c>
+      <c r="L47" s="1">
+        <v>136</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>488.5</v>
+      </c>
+      <c r="O47" s="1">
+        <v>136</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>522</v>
+      </c>
+      <c r="R47" s="1">
+        <v>136</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U47" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
